--- a/Roller.xlsx
+++ b/Roller.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Global\Desktop\Trials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E11EEB1-7F17-4B64-BF07-9B0891868405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{2E11EEB1-7F17-4B64-BF07-9B0891868405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AC52F20-BDF9-4414-BF6A-DA3FFA9DC243}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="240" windowWidth="24240" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,49 +38,49 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
+    <t>Rolls-Check</t>
+  </si>
+  <si>
+    <t>Width(m)</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>Rolls-Length</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Missing</t>
+  </si>
+  <si>
+    <t>Total-Rolls(Set)</t>
+  </si>
+  <si>
     <t>roll</t>
   </si>
   <si>
+    <t>Messured-Roll-Length(sample)</t>
+  </si>
+  <si>
+    <t>Total-Rolls-(Delivered)</t>
+  </si>
+  <si>
+    <t>Total-Rolls-(Sample)</t>
+  </si>
+  <si>
+    <t>Required-Rolls-(metre)</t>
+  </si>
+  <si>
+    <t>Required-Rolls-(Set)</t>
+  </si>
+  <si>
     <t>Tollerance</t>
   </si>
   <si>
-    <t>Missing</t>
-  </si>
-  <si>
-    <t>Messured-Roll-Length(sample)</t>
-  </si>
-  <si>
-    <t>Total-Rolls-(Delivered)</t>
-  </si>
-  <si>
-    <t>Required-Rolls-(Set)</t>
-  </si>
-  <si>
-    <t>Width(m)</t>
-  </si>
-  <si>
-    <t>Total-Rolls(Set)</t>
-  </si>
-  <si>
-    <t>Rolls-Length</t>
-  </si>
-  <si>
-    <t>Total-Rolls-(Sample)</t>
-  </si>
-  <si>
-    <t>Required-Rolls-(metre)</t>
-  </si>
-  <si>
-    <t>Rolls-Check</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>cm</t>
   </si>
 </sst>
 </file>
@@ -88,7 +90,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -560,136 +562,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.85546875" style="2" customWidth="1"/>
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="23.25">
       <c r="A1" s="8" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
     </row>
-    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1">
         <v>7.9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>29.56</v>
+        <v>29.84</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3">
         <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>24000</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>B3-B4</f>
-        <v>-0.44000000000000128</v>
+        <v>-0.16000000000000014</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>B5*B3</f>
-        <v>0</v>
+        <v>716160</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>B6*B5</f>
-        <v>0</v>
+        <v>-3840.0000000000036</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>B7-B8</f>
-        <v>0</v>
+        <v>720000</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>5</v>
       </c>
       <c r="B10" s="5">
         <f>B9/B3</f>
-        <v>0</v>
+        <v>24128.686327077747</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B11" s="6">
         <v>0.03</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="9" t="str">
         <f>IF(B2&gt;7.9,"Fail","Pass")</f>
         <v>Pass</v>
@@ -697,10 +699,10 @@
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
     </row>
-    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="12" t="str">
         <f>IF(B9 &gt; (B7*B11), "Fail", "Pass")</f>
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="14"/>
